--- a/mat_cal.xlsx
+++ b/mat_cal.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="cw" sheetId="1" state="visible" r:id="rId2"/>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">prod</t>
   </si>
   <si>
-    <t xml:space="preserve"> 283-0403-31</t>
+    <t xml:space="preserve">283-0403-31</t>
   </si>
   <si>
     <t xml:space="preserve">400G QSFP-DD DR4 GEN3</t>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">800G OSFP PSM8 Gen2.0 SiP</t>
   </si>
   <si>
-    <t xml:space="preserve"> 283-0447</t>
+    <t xml:space="preserve">283-0447</t>
   </si>
   <si>
     <t xml:space="preserve">800G OSFP DR8+ Gen2.0 SiP 2xMPO12 </t>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t xml:space="preserve">283-0396-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283-0403-31</t>
   </si>
   <si>
     <t xml:space="preserve">283-0426-31</t>
@@ -289,6 +286,12 @@
     <t xml:space="preserve">CW</t>
   </si>
   <si>
+    <t xml:space="preserve"> 283-0403-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 283-0447</t>
+  </si>
+  <si>
     <t xml:space="preserve">PIC</t>
   </si>
   <si>
@@ -359,9 +362,6 @@
   </si>
   <si>
     <t xml:space="preserve">283-0433-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283-0447</t>
   </si>
   <si>
     <t xml:space="preserve">283-0465-31</t>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B75" s="10" t="n">
         <v>1</v>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>1</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B77" s="12" t="n">
         <v>1</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B78" s="12" t="n">
         <v>2</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B79" s="12" t="n">
         <v>2</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B80" s="12" t="n">
         <v>2</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B81" s="12" t="n">
         <v>2</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B82" s="12" t="n">
         <v>2</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B83" s="12" t="n">
         <v>2</v>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B84" s="12" t="n">
         <v>2</v>
@@ -2545,7 +2545,7 @@
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B85" s="12" t="n">
         <v>3</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B86" s="12" t="n">
         <v>3</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B87" s="12" t="n">
         <v>3</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B88" s="12" t="n">
         <v>3</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B89" s="12" t="n">
         <v>3</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B90" s="12" t="n">
         <v>3</v>
@@ -2647,7 +2647,7 @@
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B91" s="12" t="n">
         <v>3</v>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B92" s="12" t="n">
         <v>3</v>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B93" s="12" t="n">
         <v>4</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B94" s="12" t="n">
         <v>5</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B95" s="12" t="n">
         <v>2</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B96" s="10" t="n">
         <v>1</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B97" s="12" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B98" s="12" t="n">
         <v>1</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B99" s="12" t="n">
         <v>2</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B100" s="12" t="n">
         <v>2</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B101" s="12" t="n">
         <v>2</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B102" s="12" t="n">
         <v>2</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B103" s="12" t="n">
         <v>2</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B104" s="12" t="n">
         <v>2</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B105" s="12" t="n">
         <v>2</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B106" s="6" t="n">
         <v>3</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B107" s="10" t="n">
         <v>3</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B108" s="12" t="n">
         <v>3</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B109" s="12" t="n">
         <v>3</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B110" s="12" t="n">
         <v>3</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B111" s="12" t="n">
         <v>3</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B112" s="12" t="n">
         <v>3</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B113" s="12" t="n">
         <v>3</v>
@@ -3038,7 +3038,7 @@
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B114" s="12" t="n">
         <v>3</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B115" s="12" t="n">
         <v>3</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B116" s="12" t="n">
         <v>3</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B117" s="12" t="n">
         <v>3</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B118" s="12" t="n">
         <v>3</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B119" s="12" t="n">
         <v>4</v>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B120" s="12" t="n">
         <v>5</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B121" s="6" t="n">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B122" s="12" t="n">
         <v>1</v>
@@ -3191,7 +3191,7 @@
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B123" s="12" t="n">
         <v>1</v>
@@ -3208,7 +3208,7 @@
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B124" s="12" t="n">
         <v>1</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B125" s="12" t="n">
         <v>1</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B126" s="12" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B127" s="12" t="n">
         <v>1</v>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B128" s="12" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B129" s="12" t="n">
         <v>1</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B130" s="12" t="n">
         <v>1</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B131" s="6" t="n">
         <v>2</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B132" s="12" t="n">
         <v>2</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B133" s="12" t="n">
         <v>2</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B134" s="12" t="n">
         <v>2</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B135" s="12" t="n">
         <v>2</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B136" s="12" t="n">
         <v>2</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B137" s="12" t="n">
         <v>2</v>
@@ -3446,7 +3446,7 @@
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B138" s="12" t="n">
         <v>2</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B139" s="10" t="n">
         <v>3</v>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B140" s="12" t="n">
         <v>3</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B141" s="12" t="n">
         <v>4</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B142" s="18" t="n">
         <v>5</v>
@@ -3555,10 +3555,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>83</v>
       </c>
       <c r="C1" s="49" t="s">
         <v>163</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="20" t="n">
         <v>1</v>
@@ -6562,10 +6562,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>50</v>
       </c>
       <c r="C3" s="23" t="n">
         <v>0</v>
@@ -6579,10 +6579,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="20" t="n">
         <v>0</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>0</v>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
@@ -6630,7 +6630,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>1</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>1</v>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>1</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="20" t="n">
         <v>1</v>
@@ -6698,7 +6698,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>2</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="20" t="n">
         <v>1</v>
@@ -6732,7 +6732,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="23" t="n">
         <v>1</v>
@@ -6749,7 +6749,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="20" t="n">
         <v>1</v>
@@ -6766,7 +6766,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="20" t="n">
         <v>1</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="20" t="n">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="20" t="n">
         <v>1</v>
@@ -6817,7 +6817,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B18" s="20" t="n">
         <v>1</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" s="20" t="n">
         <v>1</v>
@@ -6851,7 +6851,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="20" t="n">
         <v>1</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>1</v>
@@ -6885,7 +6885,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="20" t="n">
         <v>1</v>
@@ -6902,7 +6902,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>1</v>
@@ -6919,7 +6919,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>1</v>
@@ -6936,7 +6936,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>1</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" s="20" t="n">
         <v>1</v>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27" s="20" t="n">
         <v>1</v>
@@ -6987,7 +6987,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="20" t="n">
         <v>1</v>
@@ -7004,7 +7004,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B29" s="20" t="n">
         <v>1</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" s="23" t="n">
         <v>1</v>
@@ -7055,7 +7055,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>1</v>
@@ -7072,7 +7072,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" s="20" t="n">
         <v>1</v>
@@ -7089,7 +7089,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" s="20" t="n">
         <v>1</v>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>1</v>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>1</v>
@@ -7140,7 +7140,7 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B37" s="20" t="n">
         <v>1</v>
@@ -7157,7 +7157,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="20" t="n">
         <v>1</v>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="20" t="n">
         <v>1</v>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="20" t="n">
         <v>1</v>
@@ -7208,7 +7208,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" s="20" t="n">
         <v>1</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="20" t="n">
         <v>1</v>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="20" t="n">
         <v>1</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" s="20" t="n">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" s="20" t="n">
         <v>1</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B46" s="20" t="n">
         <v>1</v>
@@ -7310,7 +7310,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" s="20" t="n">
         <v>1</v>
@@ -7327,7 +7327,7 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="20" t="n">
         <v>1</v>
@@ -7344,7 +7344,7 @@
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B49" s="20" t="n">
         <v>1</v>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50" s="20" t="n">
         <v>1</v>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" s="20" t="n">
         <v>1</v>
@@ -7395,7 +7395,7 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B52" s="20" t="n">
         <v>1</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" s="20" t="n">
         <v>1</v>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" s="20" t="n">
         <v>1</v>
@@ -7446,7 +7446,7 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B55" s="23" t="n">
         <v>1</v>
@@ -7463,7 +7463,7 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="20" t="n">
         <v>1</v>
@@ -7480,7 +7480,7 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="20" t="n">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="20" t="n">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="20" t="n">
         <v>1</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="20" t="n">
         <v>1</v>
@@ -7548,7 +7548,7 @@
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="20" t="n">
         <v>1</v>
@@ -7565,7 +7565,7 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="20" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="23" t="n">
         <v>1</v>
@@ -7599,7 +7599,7 @@
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="20" t="n">
         <v>1</v>
@@ -7616,7 +7616,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="20" t="n">
         <v>1</v>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="20" t="n">
         <v>1</v>
@@ -7650,7 +7650,7 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="20" t="n">
         <v>1</v>
@@ -7667,7 +7667,7 @@
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="20" t="n">
         <v>1</v>
@@ -7684,7 +7684,7 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="20" t="n">
         <v>1</v>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B70" s="20" t="n">
         <v>1</v>
@@ -7718,7 +7718,7 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" s="20" t="n">
         <v>1</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B72" s="20" t="n">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="20" t="n">
         <v>1</v>
@@ -7769,7 +7769,7 @@
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B74" s="20" t="n">
         <v>1</v>
@@ -7786,7 +7786,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B75" s="20" t="n">
         <v>2</v>
@@ -7803,7 +7803,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="20" t="n">
         <v>2</v>
@@ -7820,7 +7820,7 @@
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="20" t="n">
         <v>2</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B78" s="20" t="n">
         <v>1</v>
@@ -7854,7 +7854,7 @@
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B79" s="20" t="n">
         <v>1</v>
@@ -7871,7 +7871,7 @@
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B80" s="20" t="n">
         <v>2</v>
@@ -7888,7 +7888,7 @@
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B81" s="20" t="n">
         <v>2</v>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B82" s="20" t="n">
         <v>4</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B83" s="23" t="n">
         <v>3</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B84" s="20" t="n">
         <v>3</v>
@@ -7956,7 +7956,7 @@
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B85" s="20" t="n">
         <v>3</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B86" s="20" t="n">
         <v>3</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B87" s="20" t="n">
         <v>3</v>
@@ -8007,7 +8007,7 @@
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B88" s="20" t="n">
         <v>3</v>
@@ -8024,7 +8024,7 @@
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B89" s="20" t="n">
         <v>1</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B90" s="20" t="n">
         <v>2</v>
@@ -8058,7 +8058,7 @@
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B91" s="20" t="n">
         <v>2</v>
@@ -8075,7 +8075,7 @@
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B92" s="20" t="n">
         <v>2</v>
@@ -8092,7 +8092,7 @@
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B93" s="20" t="n">
         <v>2</v>
@@ -8109,7 +8109,7 @@
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B94" s="20" t="n">
         <v>3</v>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B95" s="20" t="n">
         <v>3</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B96" s="20" t="n">
         <v>3</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B97" s="20" t="n">
         <v>3</v>
@@ -8177,7 +8177,7 @@
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B98" s="20" t="n">
         <v>1</v>
@@ -8194,7 +8194,7 @@
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B99" s="20" t="n">
         <v>1</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B100" s="20" t="n">
         <v>2</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B101" s="20" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B102" s="20" t="n">
         <v>2</v>
@@ -8262,7 +8262,7 @@
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B103" s="20" t="n">
         <v>2</v>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B104" s="20" t="n">
         <v>3</v>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B105" s="20" t="n">
         <v>4</v>
@@ -8313,7 +8313,7 @@
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B106" s="20" t="n">
         <v>5</v>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B107" s="20" t="n">
         <v>1</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B108" s="20" t="n">
         <v>3</v>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B109" s="20" t="n">
         <v>4</v>
@@ -8381,7 +8381,7 @@
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B110" s="20" t="n">
         <v>1</v>
@@ -8398,7 +8398,7 @@
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B111" s="20" t="n">
         <v>3</v>
@@ -8415,7 +8415,7 @@
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B112" s="20" t="n">
         <v>4</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C113" s="20" t="n">
         <v>0</v>
@@ -8449,10 +8449,10 @@
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C114" s="20" t="n">
         <v>0</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C115" s="20" t="n">
         <v>0</v>
@@ -8483,10 +8483,10 @@
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C116" s="20" t="n">
         <v>0</v>
@@ -8500,10 +8500,10 @@
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B117" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C117" s="20" t="n">
         <v>0</v>
@@ -8517,10 +8517,10 @@
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B118" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C118" s="20" t="n">
         <v>0</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B119" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C119" s="20" t="n">
         <v>0</v>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B120" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C120" s="20" t="n">
         <v>0</v>
@@ -8568,10 +8568,10 @@
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B121" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C121" s="20" t="n">
         <v>0</v>
@@ -8585,10 +8585,10 @@
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C122" s="20" t="n">
         <v>0</v>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C123" s="20" t="n">
         <v>0</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B124" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C124" s="20" t="n">
         <v>0</v>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B125" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C125" s="20" t="n">
         <v>0</v>
@@ -8653,10 +8653,10 @@
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B126" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C126" s="20" t="n">
         <v>0</v>
@@ -8694,30 +8694,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>3</v>
@@ -8734,10 +8734,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>5</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>3</v>
@@ -8754,10 +8754,10 @@
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>5</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
@@ -8774,10 +8774,10 @@
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>3</v>
@@ -8794,10 +8794,10 @@
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>3</v>
@@ -8814,10 +8814,10 @@
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>1</v>
@@ -8834,10 +8834,10 @@
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>1</v>
@@ -8854,10 +8854,10 @@
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>1</v>
@@ -8874,10 +8874,10 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>1</v>
@@ -8894,10 +8894,10 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>1</v>
@@ -8914,10 +8914,10 @@
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1</v>
@@ -8934,10 +8934,10 @@
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2</v>
@@ -8954,10 +8954,10 @@
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>1</v>
@@ -8974,13 +8974,13 @@
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="22" t="s">
         <v>49</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>50</v>
       </c>
       <c r="D15" s="23" t="n">
         <v>1</v>
@@ -8994,13 +8994,13 @@
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="20" t="n">
         <v>1</v>
@@ -9014,13 +9014,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="20" t="n">
         <v>1</v>
@@ -9034,13 +9034,13 @@
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="20" t="n">
         <v>1</v>
@@ -9054,10 +9054,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="20" t="n">
         <v>1</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="20" t="n">
         <v>1</v>
@@ -9094,10 +9094,10 @@
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="20" t="n">
         <v>1</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="20" t="n">
         <v>1</v>
@@ -9134,10 +9134,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="20" t="n">
         <v>2</v>
@@ -9154,10 +9154,10 @@
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="20" t="n">
         <v>1</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" s="23" t="n">
         <v>1</v>
@@ -9194,10 +9194,10 @@
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="20" t="n">
         <v>1</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="20" t="n">
         <v>1</v>
@@ -9234,10 +9234,10 @@
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="20" t="n">
         <v>1</v>
@@ -9254,10 +9254,10 @@
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29" s="20" t="n">
         <v>1</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="20" t="n">
         <v>1</v>
@@ -9294,10 +9294,10 @@
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="20" t="n">
         <v>1</v>
@@ -9314,10 +9314,10 @@
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="20" t="n">
         <v>1</v>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" s="20" t="n">
         <v>1</v>
@@ -9354,10 +9354,10 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="20" t="n">
         <v>1</v>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C35" s="20" t="n">
         <v>1</v>
@@ -9394,10 +9394,10 @@
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="20" t="n">
         <v>1</v>
@@ -9414,10 +9414,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="20" t="n">
         <v>1</v>
@@ -9434,10 +9434,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="20" t="n">
         <v>1</v>
@@ -9454,10 +9454,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="20" t="n">
         <v>1</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="20" t="n">
         <v>1</v>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" s="20" t="n">
         <v>1</v>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="20" t="n">
         <v>1</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43" s="23" t="n">
         <v>1</v>
@@ -9554,10 +9554,10 @@
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C44" s="20" t="n">
         <v>1</v>
@@ -9574,10 +9574,10 @@
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" s="20" t="n">
         <v>1</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C46" s="20" t="n">
         <v>1</v>
@@ -9614,10 +9614,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C47" s="20" t="n">
         <v>1</v>
@@ -9634,10 +9634,10 @@
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" s="20" t="n">
         <v>1</v>
@@ -9654,10 +9654,10 @@
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="20" t="n">
         <v>1</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" s="20" t="n">
         <v>1</v>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="20" t="n">
         <v>1</v>
@@ -9714,10 +9714,10 @@
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="20" t="n">
         <v>1</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" s="20" t="n">
         <v>1</v>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" s="20" t="n">
         <v>1</v>
@@ -9774,10 +9774,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" s="20" t="n">
         <v>1</v>
@@ -9794,10 +9794,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="20" t="n">
         <v>1</v>
@@ -9814,10 +9814,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="20" t="n">
         <v>1</v>
@@ -9834,10 +9834,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" s="20" t="n">
         <v>1</v>
@@ -9854,10 +9854,10 @@
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C59" s="20" t="n">
         <v>1</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" s="20" t="n">
         <v>1</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" s="20" t="n">
         <v>1</v>
@@ -9914,10 +9914,10 @@
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62" s="20" t="n">
         <v>1</v>
@@ -9934,10 +9934,10 @@
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" s="20" t="n">
         <v>1</v>
@@ -9954,10 +9954,10 @@
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" s="20" t="n">
         <v>1</v>
@@ -9974,10 +9974,10 @@
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C65" s="20" t="n">
         <v>1</v>
@@ -9994,10 +9994,10 @@
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C66" s="20" t="n">
         <v>1</v>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C67" s="23" t="n">
         <v>1</v>
@@ -10034,10 +10034,10 @@
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C68" s="20" t="n">
         <v>1</v>
@@ -10054,10 +10054,10 @@
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C69" s="20" t="n">
         <v>1</v>
@@ -10074,10 +10074,10 @@
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C70" s="20" t="n">
         <v>1</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C71" s="20" t="n">
         <v>1</v>
@@ -10114,10 +10114,10 @@
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C72" s="20" t="n">
         <v>1</v>
@@ -10134,10 +10134,10 @@
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C73" s="20" t="n">
         <v>1</v>
@@ -10154,10 +10154,10 @@
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C74" s="20" t="n">
         <v>1</v>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C75" s="23" t="n">
         <v>1</v>
@@ -10194,10 +10194,10 @@
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C76" s="20" t="n">
         <v>1</v>
@@ -10214,10 +10214,10 @@
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="20" t="n">
         <v>1</v>
@@ -10234,10 +10234,10 @@
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C78" s="20" t="n">
         <v>1</v>
@@ -10254,10 +10254,10 @@
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C79" s="20" t="n">
         <v>1</v>
@@ -10274,10 +10274,10 @@
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C80" s="20" t="n">
         <v>1</v>
@@ -10294,10 +10294,10 @@
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C81" s="20" t="n">
         <v>1</v>
@@ -10314,10 +10314,10 @@
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" s="20" t="n">
         <v>1</v>
@@ -10334,10 +10334,10 @@
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C83" s="20" t="n">
         <v>1</v>
@@ -10354,10 +10354,10 @@
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C84" s="20" t="n">
         <v>1</v>
@@ -10374,10 +10374,10 @@
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C85" s="20" t="n">
         <v>1</v>
@@ -10394,10 +10394,10 @@
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C86" s="20" t="n">
         <v>1</v>
@@ -10414,10 +10414,10 @@
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C87" s="20" t="n">
         <v>2</v>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C88" s="20" t="n">
         <v>2</v>
@@ -10454,10 +10454,10 @@
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C89" s="20" t="n">
         <v>2</v>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C90" s="20" t="n">
         <v>1</v>
@@ -10494,10 +10494,10 @@
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C91" s="20" t="n">
         <v>1</v>
@@ -10514,10 +10514,10 @@
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C92" s="20" t="n">
         <v>2</v>
@@ -10534,10 +10534,10 @@
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C93" s="20" t="n">
         <v>2</v>
@@ -10554,10 +10554,10 @@
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C94" s="20" t="n">
         <v>4</v>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C95" s="23" t="n">
         <v>3</v>
@@ -10594,10 +10594,10 @@
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C96" s="20" t="n">
         <v>3</v>
@@ -10614,10 +10614,10 @@
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C97" s="20" t="n">
         <v>3</v>
@@ -10634,10 +10634,10 @@
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C98" s="20" t="n">
         <v>3</v>
@@ -10654,10 +10654,10 @@
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C99" s="20" t="n">
         <v>3</v>
@@ -10674,10 +10674,10 @@
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C100" s="20" t="n">
         <v>3</v>
@@ -10694,10 +10694,10 @@
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C101" s="20" t="n">
         <v>1</v>
@@ -10714,10 +10714,10 @@
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C102" s="20" t="n">
         <v>2</v>
@@ -10734,10 +10734,10 @@
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C103" s="20" t="n">
         <v>2</v>
@@ -10754,10 +10754,10 @@
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C104" s="20" t="n">
         <v>2</v>
@@ -10774,10 +10774,10 @@
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C105" s="20" t="n">
         <v>2</v>
@@ -10794,10 +10794,10 @@
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B106" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C106" s="20" t="n">
         <v>3</v>
@@ -10814,10 +10814,10 @@
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B107" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C107" s="20" t="n">
         <v>3</v>
@@ -10834,10 +10834,10 @@
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B108" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C108" s="20" t="n">
         <v>3</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B109" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C109" s="20" t="n">
         <v>3</v>
@@ -10874,10 +10874,10 @@
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B110" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C110" s="20" t="n">
         <v>1</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B111" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C111" s="20" t="n">
         <v>1</v>
@@ -10914,10 +10914,10 @@
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B112" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C112" s="20" t="n">
         <v>2</v>
@@ -10934,10 +10934,10 @@
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B113" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C113" s="20" t="n">
         <v>2</v>
@@ -10954,10 +10954,10 @@
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B114" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C114" s="20" t="n">
         <v>2</v>
@@ -10974,10 +10974,10 @@
     </row>
     <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B115" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C115" s="20" t="n">
         <v>2</v>
@@ -10994,10 +10994,10 @@
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B116" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C116" s="20" t="n">
         <v>3</v>
@@ -11014,10 +11014,10 @@
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B117" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C117" s="20" t="n">
         <v>4</v>
@@ -11034,10 +11034,10 @@
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B118" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C118" s="20" t="n">
         <v>5</v>
@@ -11054,10 +11054,10 @@
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B119" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C119" s="20" t="n">
         <v>1</v>
@@ -11074,10 +11074,10 @@
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B120" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C120" s="20" t="n">
         <v>3</v>
@@ -11094,10 +11094,10 @@
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B121" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C121" s="20" t="n">
         <v>4</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B122" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C122" s="20" t="n">
         <v>1</v>
@@ -11134,10 +11134,10 @@
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B123" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C123" s="20" t="n">
         <v>3</v>
@@ -11154,10 +11154,10 @@
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B124" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C124" s="20" t="n">
         <v>4</v>
@@ -11174,13 +11174,13 @@
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B125" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C125" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D125" s="20" t="n">
         <v>1</v>
@@ -11194,13 +11194,13 @@
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B126" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C126" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D126" s="20" t="n">
         <v>1</v>
@@ -11214,13 +11214,13 @@
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B127" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C127" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D127" s="20" t="n">
         <v>1</v>
@@ -11234,13 +11234,13 @@
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B128" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C128" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D128" s="20" t="n">
         <v>1</v>
@@ -11254,13 +11254,13 @@
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B129" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C129" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D129" s="20" t="n">
         <v>1</v>
@@ -11274,13 +11274,13 @@
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B130" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C130" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D130" s="20" t="n">
         <v>1</v>
@@ -11294,13 +11294,13 @@
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B131" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D131" s="20" t="n">
         <v>1</v>
@@ -11314,13 +11314,13 @@
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B132" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C132" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D132" s="20" t="n">
         <v>1</v>
@@ -11334,13 +11334,13 @@
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B133" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C133" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D133" s="20" t="n">
         <v>1</v>
@@ -11354,13 +11354,13 @@
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C134" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D134" s="20" t="n">
         <v>1</v>
@@ -11374,13 +11374,13 @@
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B135" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C135" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D135" s="20" t="n">
         <v>1</v>
@@ -11394,13 +11394,13 @@
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B136" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C136" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D136" s="20" t="n">
         <v>1</v>
@@ -11414,13 +11414,13 @@
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B137" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C137" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D137" s="20" t="n">
         <v>1</v>
@@ -11434,13 +11434,13 @@
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B138" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C138" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D138" s="20" t="n">
         <v>1</v>
@@ -11454,7 +11454,7 @@
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B139" s="14" t="s">
         <v>16</v>
@@ -11474,7 +11474,7 @@
     </row>
     <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B140" s="9" t="s">
         <v>16</v>
@@ -11494,7 +11494,7 @@
     </row>
     <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>16</v>
@@ -11514,7 +11514,7 @@
     </row>
     <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>16</v>
@@ -11534,7 +11534,7 @@
     </row>
     <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>16</v>
@@ -11554,7 +11554,7 @@
     </row>
     <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>16</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>16</v>
@@ -11594,7 +11594,7 @@
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>16</v>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B147" s="14" t="s">
         <v>19</v>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B148" s="14" t="s">
         <v>19</v>
@@ -11654,7 +11654,7 @@
     </row>
     <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B149" s="14" t="s">
         <v>19</v>
@@ -11674,7 +11674,7 @@
     </row>
     <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B150" s="14" t="s">
         <v>19</v>
@@ -11694,7 +11694,7 @@
     </row>
     <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B151" s="14" t="s">
         <v>19</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B152" s="14" t="s">
         <v>19</v>
@@ -11734,7 +11734,7 @@
     </row>
     <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B153" s="14" t="s">
         <v>19</v>
@@ -11754,7 +11754,7 @@
     </row>
     <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B154" s="14" t="s">
         <v>19</v>
@@ -11774,7 +11774,7 @@
     </row>
     <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B155" s="14" t="s">
         <v>19</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B156" s="14" t="s">
         <v>19</v>
@@ -11814,7 +11814,7 @@
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B157" s="16" t="s">
         <v>19</v>
@@ -11834,7 +11834,7 @@
     </row>
     <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B158" s="14" t="s">
         <v>19</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B159" s="14" t="s">
         <v>19</v>
@@ -11874,7 +11874,7 @@
     </row>
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>19</v>
@@ -11894,7 +11894,7 @@
     </row>
     <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B161" s="14" t="s">
         <v>19</v>
@@ -11914,7 +11914,7 @@
     </row>
     <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B162" s="14" t="s">
         <v>19</v>
@@ -11934,7 +11934,7 @@
     </row>
     <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B163" s="14" t="s">
         <v>19</v>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B164" s="14" t="s">
         <v>19</v>
@@ -11974,7 +11974,7 @@
     </row>
     <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>19</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B166" s="9" t="s">
         <v>19</v>
@@ -12014,7 +12014,7 @@
     </row>
     <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>19</v>
@@ -12034,7 +12034,7 @@
     </row>
     <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>19</v>
@@ -12054,7 +12054,7 @@
     </row>
     <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B169" s="14" t="s">
         <v>19</v>
@@ -12074,7 +12074,7 @@
     </row>
     <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B170" s="14" t="s">
         <v>19</v>
@@ -12094,7 +12094,7 @@
     </row>
     <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B171" s="14" t="s">
         <v>19</v>
@@ -12114,7 +12114,7 @@
     </row>
     <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B172" s="14" t="s">
         <v>19</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B173" s="14" t="s">
         <v>19</v>
@@ -12154,7 +12154,7 @@
     </row>
     <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>39</v>
@@ -12174,7 +12174,7 @@
     </row>
     <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>39</v>
@@ -12194,7 +12194,7 @@
     </row>
     <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>39</v>
@@ -12214,7 +12214,7 @@
     </row>
     <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>39</v>
@@ -12234,7 +12234,7 @@
     </row>
     <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>39</v>
@@ -12254,7 +12254,7 @@
     </row>
     <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>39</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>39</v>
@@ -12294,7 +12294,7 @@
     </row>
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>39</v>
@@ -12314,7 +12314,7 @@
     </row>
     <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>39</v>
@@ -12334,7 +12334,7 @@
     </row>
     <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>39</v>
@@ -12354,7 +12354,7 @@
     </row>
     <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>39</v>
@@ -12374,7 +12374,7 @@
     </row>
     <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>39</v>
@@ -12394,7 +12394,7 @@
     </row>
     <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B186" s="9" t="s">
         <v>39</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>39</v>
@@ -12434,7 +12434,7 @@
     </row>
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>39</v>
@@ -12454,7 +12454,7 @@
     </row>
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>39</v>
@@ -12474,7 +12474,7 @@
     </row>
     <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B190" s="14" t="s">
         <v>41</v>
@@ -12494,7 +12494,7 @@
     </row>
     <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B191" s="14" t="s">
         <v>41</v>
@@ -12514,7 +12514,7 @@
     </row>
     <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B192" s="14" t="s">
         <v>41</v>
@@ -12534,7 +12534,7 @@
     </row>
     <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>41</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>42</v>
@@ -12574,7 +12574,7 @@
     </row>
     <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>42</v>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>42</v>
@@ -12614,7 +12614,7 @@
     </row>
     <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>42</v>
@@ -12634,7 +12634,7 @@
     </row>
     <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>42</v>
@@ -12654,7 +12654,7 @@
     </row>
     <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>42</v>
@@ -12674,10 +12674,10 @@
     </row>
     <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C200" s="10" t="n">
         <v>1</v>
@@ -12694,10 +12694,10 @@
     </row>
     <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C201" s="12" t="n">
         <v>1</v>
@@ -12714,10 +12714,10 @@
     </row>
     <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C202" s="12" t="n">
         <v>1</v>
@@ -12734,10 +12734,10 @@
     </row>
     <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C203" s="12" t="n">
         <v>2</v>
@@ -12754,10 +12754,10 @@
     </row>
     <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C204" s="12" t="n">
         <v>2</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C205" s="12" t="n">
         <v>2</v>
@@ -12794,10 +12794,10 @@
     </row>
     <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C206" s="12" t="n">
         <v>2</v>
@@ -12814,10 +12814,10 @@
     </row>
     <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C207" s="12" t="n">
         <v>2</v>
@@ -12834,10 +12834,10 @@
     </row>
     <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C208" s="12" t="n">
         <v>2</v>
@@ -12854,10 +12854,10 @@
     </row>
     <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C209" s="12" t="n">
         <v>2</v>
@@ -12874,10 +12874,10 @@
     </row>
     <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C210" s="12" t="n">
         <v>3</v>
@@ -12894,10 +12894,10 @@
     </row>
     <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C211" s="12" t="n">
         <v>3</v>
@@ -12914,10 +12914,10 @@
     </row>
     <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C212" s="12" t="n">
         <v>3</v>
@@ -12934,10 +12934,10 @@
     </row>
     <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C213" s="12" t="n">
         <v>3</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C214" s="12" t="n">
         <v>3</v>
@@ -12974,10 +12974,10 @@
     </row>
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C215" s="12" t="n">
         <v>3</v>
@@ -12994,10 +12994,10 @@
     </row>
     <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C216" s="12" t="n">
         <v>3</v>
@@ -13014,10 +13014,10 @@
     </row>
     <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C217" s="12" t="n">
         <v>3</v>
@@ -13034,10 +13034,10 @@
     </row>
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C218" s="12" t="n">
         <v>4</v>
@@ -13054,10 +13054,10 @@
     </row>
     <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C219" s="12" t="n">
         <v>5</v>
@@ -13074,10 +13074,10 @@
     </row>
     <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C220" s="12" t="n">
         <v>2</v>
@@ -13094,10 +13094,10 @@
     </row>
     <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C221" s="10" t="n">
         <v>1</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C222" s="12" t="n">
         <v>1</v>
@@ -13134,10 +13134,10 @@
     </row>
     <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C223" s="12" t="n">
         <v>1</v>
@@ -13154,10 +13154,10 @@
     </row>
     <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C224" s="12" t="n">
         <v>2</v>
@@ -13174,10 +13174,10 @@
     </row>
     <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C225" s="12" t="n">
         <v>2</v>
@@ -13194,10 +13194,10 @@
     </row>
     <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C226" s="12" t="n">
         <v>2</v>
@@ -13214,10 +13214,10 @@
     </row>
     <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C227" s="12" t="n">
         <v>2</v>
@@ -13234,10 +13234,10 @@
     </row>
     <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C228" s="12" t="n">
         <v>2</v>
@@ -13254,10 +13254,10 @@
     </row>
     <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C229" s="12" t="n">
         <v>2</v>
@@ -13274,10 +13274,10 @@
     </row>
     <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C230" s="12" t="n">
         <v>2</v>
@@ -13294,10 +13294,10 @@
     </row>
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C231" s="6" t="n">
         <v>3</v>
@@ -13314,10 +13314,10 @@
     </row>
     <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C232" s="10" t="n">
         <v>3</v>
@@ -13334,10 +13334,10 @@
     </row>
     <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C233" s="12" t="n">
         <v>3</v>
@@ -13354,10 +13354,10 @@
     </row>
     <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C234" s="12" t="n">
         <v>3</v>
@@ -13374,10 +13374,10 @@
     </row>
     <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C235" s="12" t="n">
         <v>3</v>
@@ -13394,10 +13394,10 @@
     </row>
     <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C236" s="12" t="n">
         <v>3</v>
@@ -13414,10 +13414,10 @@
     </row>
     <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C237" s="12" t="n">
         <v>3</v>
@@ -13434,10 +13434,10 @@
     </row>
     <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C238" s="12" t="n">
         <v>3</v>
@@ -13454,10 +13454,10 @@
     </row>
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C239" s="12" t="n">
         <v>3</v>
@@ -13474,10 +13474,10 @@
     </row>
     <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C240" s="12" t="n">
         <v>3</v>
@@ -13494,10 +13494,10 @@
     </row>
     <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C241" s="12" t="n">
         <v>3</v>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C242" s="12" t="n">
         <v>3</v>
@@ -13534,10 +13534,10 @@
     </row>
     <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C243" s="12" t="n">
         <v>3</v>
@@ -13554,10 +13554,10 @@
     </row>
     <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C244" s="12" t="n">
         <v>4</v>
@@ -13574,10 +13574,10 @@
     </row>
     <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C245" s="12" t="n">
         <v>5</v>
@@ -13594,10 +13594,10 @@
     </row>
     <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C246" s="6" t="n">
         <v>1</v>
@@ -13614,10 +13614,10 @@
     </row>
     <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C247" s="12" t="n">
         <v>1</v>
@@ -13634,10 +13634,10 @@
     </row>
     <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C248" s="12" t="n">
         <v>1</v>
@@ -13654,10 +13654,10 @@
     </row>
     <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C249" s="12" t="n">
         <v>1</v>
@@ -13674,10 +13674,10 @@
     </row>
     <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C250" s="12" t="n">
         <v>1</v>
@@ -13694,10 +13694,10 @@
     </row>
     <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C251" s="12" t="n">
         <v>2</v>
@@ -13714,10 +13714,10 @@
     </row>
     <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C252" s="12" t="n">
         <v>1</v>
@@ -13734,10 +13734,10 @@
     </row>
     <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C253" s="12" t="n">
         <v>1</v>
@@ -13754,10 +13754,10 @@
     </row>
     <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C254" s="12" t="n">
         <v>1</v>
@@ -13774,10 +13774,10 @@
     </row>
     <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C255" s="12" t="n">
         <v>1</v>
@@ -13794,10 +13794,10 @@
     </row>
     <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C256" s="6" t="n">
         <v>2</v>
@@ -13814,10 +13814,10 @@
     </row>
     <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C257" s="12" t="n">
         <v>2</v>
@@ -13834,10 +13834,10 @@
     </row>
     <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C258" s="12" t="n">
         <v>2</v>
@@ -13854,10 +13854,10 @@
     </row>
     <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C259" s="12" t="n">
         <v>2</v>
@@ -13874,10 +13874,10 @@
     </row>
     <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C260" s="12" t="n">
         <v>2</v>
@@ -13894,10 +13894,10 @@
     </row>
     <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C261" s="12" t="n">
         <v>2</v>
@@ -13914,10 +13914,10 @@
     </row>
     <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C262" s="12" t="n">
         <v>2</v>
@@ -13934,10 +13934,10 @@
     </row>
     <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C263" s="12" t="n">
         <v>2</v>
@@ -13954,10 +13954,10 @@
     </row>
     <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C264" s="10" t="n">
         <v>3</v>
@@ -13974,10 +13974,10 @@
     </row>
     <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C265" s="12" t="n">
         <v>3</v>
@@ -13994,10 +13994,10 @@
     </row>
     <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C266" s="12" t="n">
         <v>4</v>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C267" s="18" t="n">
         <v>5</v>
@@ -14064,43 +14064,43 @@
         <v>4</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H1" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J1" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K1" s="29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L1" s="29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M1" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N1" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O1" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15449,43 +15449,43 @@
         <v>4</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H1" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J1" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K1" s="29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L1" s="29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M1" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N1" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O1" s="29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16922,51 +16922,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" s="33" t="s">
         <v>99</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="34" t="n">
         <v>0</v>
@@ -17013,7 +17013,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="34" t="n">
         <v>0</v>
@@ -17060,7 +17060,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" s="36" t="n">
         <v>0</v>
@@ -17107,7 +17107,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="36" t="n">
         <v>0</v>
@@ -17154,7 +17154,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="36" t="n">
         <v>62112</v>
@@ -17201,7 +17201,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="36" t="n">
         <v>0</v>
@@ -17248,7 +17248,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="36" t="n">
         <v>0</v>
@@ -17295,7 +17295,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="38" t="n">
         <v>15479</v>
@@ -17342,7 +17342,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="38" t="n">
         <v>147024</v>
@@ -17389,7 +17389,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="38" t="n">
         <v>2882</v>
@@ -17436,7 +17436,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="38" t="n">
         <v>0</v>
@@ -17483,7 +17483,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="34" t="n">
         <v>0</v>
@@ -17530,7 +17530,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" s="34" t="n">
         <v>0</v>
@@ -17577,7 +17577,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" s="34" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="34" t="n">
         <v>0</v>
@@ -17671,7 +17671,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="34" t="n">
         <v>100</v>
@@ -17718,7 +17718,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="34" t="n">
         <v>100</v>
@@ -17765,7 +17765,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="34" t="n">
         <v>71579</v>
@@ -17812,7 +17812,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="34" t="n">
         <v>187001</v>
@@ -17859,7 +17859,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B21" s="38" t="n">
         <v>151641</v>
@@ -17906,7 +17906,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="38" t="n">
         <v>44500</v>
@@ -17953,7 +17953,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="38" t="n">
         <v>0</v>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" s="38" t="n">
         <v>0</v>
@@ -18047,7 +18047,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25" s="34" t="n">
         <v>247853</v>
@@ -18094,7 +18094,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B26" s="34" t="n">
         <v>0</v>
@@ -18141,7 +18141,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B27" s="34" t="n">
         <v>0</v>
@@ -18188,7 +18188,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B28" s="34" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="34" t="n">
         <v>0</v>
@@ -18282,7 +18282,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="34" t="n">
         <v>0</v>
@@ -18329,7 +18329,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="40" t="n">
         <v>0</v>
@@ -18376,7 +18376,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="40" t="n">
         <v>0</v>
@@ -18423,7 +18423,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="34" t="n">
         <v>0</v>
@@ -18470,7 +18470,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="34" t="n">
         <v>0</v>
@@ -18517,7 +18517,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="34" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36" s="34" t="n">
         <v>0</v>
@@ -18611,7 +18611,7 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" s="34" t="n">
         <v>7628</v>
@@ -18658,7 +18658,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" s="34" t="n">
         <v>0</v>
@@ -18727,46 +18727,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="O1" s="33" t="s">
         <v>99</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18818,7 +18818,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" s="34" t="n">
         <v>198649</v>
@@ -18865,7 +18865,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B4" s="34" t="n">
         <v>0</v>
@@ -19006,7 +19006,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="34" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="B7" s="34" t="n">
         <v>357012</v>
@@ -19053,7 +19053,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="34" t="n">
         <v>2598</v>
@@ -19147,7 +19147,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="34" t="n">
         <v>445825</v>
@@ -19241,7 +19241,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="34" t="n">
         <v>0</v>
@@ -19463,7 +19463,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>116</v>
@@ -19478,7 +19478,7 @@
         <v>119</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I9" s="33" t="s">
         <v>120</v>
@@ -19493,7 +19493,7 @@
         <v>123</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N9" s="33" t="s">
         <v>124</v>
@@ -19508,37 +19508,37 @@
         <v>127</v>
       </c>
       <c r="R9" s="33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T9" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U9" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V9" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W9" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X9" s="33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z9" s="33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA9" s="33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AB9" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19633,7 +19633,7 @@
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44"/>
       <c r="B11" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="34" t="n">
         <v>198649</v>
@@ -19720,7 +19720,7 @@
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44"/>
       <c r="B12" s="34" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C12" s="34" t="n">
         <v>0</v>
@@ -19979,7 +19979,7 @@
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="44"/>
       <c r="B15" s="34" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C15" s="34" t="n">
         <v>357012</v>
@@ -20064,7 +20064,7 @@
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="44"/>
       <c r="B16" s="41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="34" t="n">
         <v>2598</v>
@@ -20238,7 +20238,7 @@
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="44"/>
       <c r="B18" s="34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="34" t="n">
         <v>445825</v>
@@ -20412,7 +20412,7 @@
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="44"/>
       <c r="B20" s="34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="34" t="n">
         <v>0</v>
@@ -20672,10 +20672,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="34" t="n">
         <v>0</v>
@@ -20762,7 +20762,7 @@
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="45"/>
       <c r="B24" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="34" t="n">
         <v>0</v>
@@ -20849,7 +20849,7 @@
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="45"/>
       <c r="B25" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" s="36" t="n">
         <v>0</v>
@@ -20936,7 +20936,7 @@
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="45"/>
       <c r="B26" s="35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C26" s="36" t="n">
         <v>0</v>
@@ -21023,7 +21023,7 @@
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="45"/>
       <c r="B27" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="36" t="n">
         <v>62112</v>
@@ -21110,7 +21110,7 @@
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="45"/>
       <c r="B28" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" s="36" t="n">
         <v>0</v>
@@ -21197,7 +21197,7 @@
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="45"/>
       <c r="B29" s="35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" s="36" t="n">
         <v>0</v>
@@ -21284,7 +21284,7 @@
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="45"/>
       <c r="B30" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C30" s="38" t="n">
         <v>15479</v>
@@ -21371,7 +21371,7 @@
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="45"/>
       <c r="B31" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" s="38" t="n">
         <v>147024</v>
@@ -21458,7 +21458,7 @@
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="45"/>
       <c r="B32" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="38" t="n">
         <v>2882</v>
@@ -21545,7 +21545,7 @@
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="45"/>
       <c r="B33" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="38" t="n">
         <v>0</v>
@@ -21632,7 +21632,7 @@
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="45"/>
       <c r="B34" s="39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="34" t="n">
         <v>0</v>
@@ -21719,7 +21719,7 @@
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="45"/>
       <c r="B35" s="39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="34" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="45"/>
       <c r="B36" s="39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="34" t="n">
         <v>0</v>
@@ -21893,7 +21893,7 @@
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="45"/>
       <c r="B37" s="39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" s="34" t="n">
         <v>0</v>
@@ -21980,7 +21980,7 @@
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="45"/>
       <c r="B38" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="34" t="n">
         <v>71579</v>
@@ -22067,7 +22067,7 @@
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="45"/>
       <c r="B39" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="34" t="n">
         <v>187001</v>
@@ -22154,7 +22154,7 @@
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="45"/>
       <c r="B40" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C40" s="38" t="n">
         <v>151641</v>
@@ -22241,7 +22241,7 @@
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="45"/>
       <c r="B41" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C41" s="38" t="n">
         <v>44500</v>
@@ -22328,7 +22328,7 @@
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="45"/>
       <c r="B42" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C42" s="38" t="n">
         <v>0</v>
@@ -22415,7 +22415,7 @@
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="45"/>
       <c r="B43" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="38" t="n">
         <v>0</v>
@@ -22501,10 +22501,10 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" s="34" t="n">
         <v>247853</v>
@@ -22591,7 +22591,7 @@
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="45"/>
       <c r="B45" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" s="34" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="45"/>
       <c r="B46" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C46" s="34" t="n">
         <v>0</v>
@@ -22765,7 +22765,7 @@
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="45"/>
       <c r="B47" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C47" s="34" t="n">
         <v>0</v>
@@ -22852,7 +22852,7 @@
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="45"/>
       <c r="B48" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C48" s="34" t="n">
         <v>0</v>
@@ -22939,7 +22939,7 @@
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="45"/>
       <c r="B49" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C49" s="34" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="45"/>
       <c r="B50" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" s="40" t="n">
         <v>0</v>
@@ -23113,7 +23113,7 @@
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="45"/>
       <c r="B51" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="40" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="45"/>
       <c r="B52" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="34" t="n">
         <v>0</v>
@@ -23287,7 +23287,7 @@
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="45"/>
       <c r="B53" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" s="34" t="n">
         <v>0</v>
@@ -23374,7 +23374,7 @@
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="45"/>
       <c r="B54" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C54" s="34" t="n">
         <v>0</v>
@@ -23461,7 +23461,7 @@
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="45"/>
       <c r="B55" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" s="34" t="n">
         <v>0</v>
@@ -23548,7 +23548,7 @@
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="45"/>
       <c r="B56" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C56" s="34" t="n">
         <v>7628</v>
@@ -23635,7 +23635,7 @@
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="45"/>
       <c r="B57" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C57" s="34" t="n">
         <v>0</v>
@@ -24500,7 +24500,7 @@
     </row>
     <row r="9" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>129</v>
@@ -24694,7 +24694,7 @@
         <v>144</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" s="34" t="n">
         <v>198649</v>
@@ -24772,7 +24772,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D13" s="34" t="n">
         <v>-36507</v>
@@ -25004,7 +25004,7 @@
         <v>147</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>357012</v>
@@ -25080,7 +25080,7 @@
         <v>148</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="34" t="n">
         <v>2598</v>
@@ -25236,7 +25236,7 @@
         <v>149</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="34" t="n">
         <v>445825</v>
@@ -25392,7 +25392,7 @@
         <v>149</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" s="34" t="n">
         <v>-636</v>
@@ -25622,13 +25622,13 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>152</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="34" t="n">
         <v>0</v>
@@ -25706,7 +25706,7 @@
         <v>152</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="34" t="n">
         <v>0</v>
@@ -25784,7 +25784,7 @@
         <v>153</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" s="36" t="n">
         <v>0</v>
@@ -25862,7 +25862,7 @@
         <v>153</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D27" s="36" t="n">
         <v>0</v>
@@ -25940,7 +25940,7 @@
         <v>153</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="36" t="n">
         <v>62112</v>
@@ -26018,7 +26018,7 @@
         <v>153</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D29" s="36" t="n">
         <v>0</v>
@@ -26096,7 +26096,7 @@
         <v>153</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D30" s="36" t="n">
         <v>0</v>
@@ -26174,7 +26174,7 @@
         <v>154</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D31" s="38" t="n">
         <v>15479</v>
@@ -26252,7 +26252,7 @@
         <v>155</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" s="38" t="n">
         <v>147024</v>
@@ -26330,7 +26330,7 @@
         <v>156</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" s="38" t="n">
         <v>2882</v>
@@ -26408,7 +26408,7 @@
         <v>156</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D34" s="38" t="n">
         <v>0</v>
@@ -26486,7 +26486,7 @@
         <v>157</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35" s="34" t="n">
         <v>0</v>
@@ -26564,7 +26564,7 @@
         <v>157</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D36" s="34" t="n">
         <v>0</v>
@@ -26642,7 +26642,7 @@
         <v>157</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D37" s="34" t="n">
         <v>0</v>
@@ -26720,7 +26720,7 @@
         <v>157</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D38" s="34" t="n">
         <v>0</v>
@@ -26798,7 +26798,7 @@
         <v>157</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="34" t="n">
         <v>71579</v>
@@ -26876,7 +26876,7 @@
         <v>157</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D40" s="34" t="n">
         <v>187001</v>
@@ -26954,7 +26954,7 @@
         <v>158</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D41" s="38" t="n">
         <v>151641</v>
@@ -27032,7 +27032,7 @@
         <v>159</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D42" s="38" t="n">
         <v>44500</v>
@@ -27110,7 +27110,7 @@
         <v>160</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D43" s="38" t="n">
         <v>0</v>
@@ -27188,7 +27188,7 @@
         <v>160</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="38" t="n">
         <v>0</v>
@@ -27262,13 +27262,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B45" s="40" t="s">
         <v>161</v>
       </c>
       <c r="C45" s="40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D45" s="34" t="n">
         <v>247853</v>
@@ -27346,7 +27346,7 @@
         <v>161</v>
       </c>
       <c r="C46" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46" s="34" t="n">
         <v>0</v>
@@ -27424,7 +27424,7 @@
         <v>161</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D47" s="34" t="n">
         <v>0</v>
@@ -27502,7 +27502,7 @@
         <v>161</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D48" s="34" t="n">
         <v>0</v>
@@ -27580,7 +27580,7 @@
         <v>161</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D49" s="34" t="n">
         <v>0</v>
@@ -27658,7 +27658,7 @@
         <v>161</v>
       </c>
       <c r="C50" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D50" s="34" t="n">
         <v>0</v>
@@ -27736,7 +27736,7 @@
         <v>161</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D51" s="40" t="n">
         <v>0</v>
@@ -27814,7 +27814,7 @@
         <v>161</v>
       </c>
       <c r="C52" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D52" s="40" t="n">
         <v>0</v>
@@ -27892,7 +27892,7 @@
         <v>161</v>
       </c>
       <c r="C53" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D53" s="34" t="n">
         <v>0</v>
@@ -27970,7 +27970,7 @@
         <v>161</v>
       </c>
       <c r="C54" s="40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D54" s="34" t="n">
         <v>0</v>
@@ -28048,7 +28048,7 @@
         <v>161</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D55" s="34" t="n">
         <v>0</v>
@@ -28126,7 +28126,7 @@
         <v>161</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D56" s="34" t="n">
         <v>0</v>
@@ -28204,7 +28204,7 @@
         <v>162</v>
       </c>
       <c r="C57" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D57" s="34" t="n">
         <v>7628</v>
@@ -28282,7 +28282,7 @@
         <v>162</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D58" s="34" t="n">
         <v>0</v>
